--- a/artfynd/A 53426-2025 artfynd.xlsx
+++ b/artfynd/A 53426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723271</v>
+        <v>127723573</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443238</v>
+        <v>443275</v>
       </c>
       <c r="R2" t="n">
-        <v>6767435</v>
+        <v>6767333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127722972</v>
+        <v>127736009</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443230</v>
+        <v>443242</v>
       </c>
       <c r="R3" t="n">
-        <v>6767432</v>
+        <v>6767240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,9 +840,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723269</v>
+        <v>127723066</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443225</v>
+        <v>443271</v>
       </c>
       <c r="R4" t="n">
-        <v>6767423</v>
+        <v>6767289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,7 +939,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722899</v>
+        <v>127730330</v>
       </c>
       <c r="B5" t="n">
-        <v>57681</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,39 +987,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443227</v>
+        <v>443272</v>
       </c>
       <c r="R5" t="n">
-        <v>6767432</v>
+        <v>6767198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,7 +1047,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1055,28 +1066,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127736025</v>
+        <v>127795268</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1096,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443175</v>
+        <v>443214</v>
       </c>
       <c r="R6" t="n">
-        <v>6767298</v>
+        <v>6767263</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1141,53 +1160,44 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127736030</v>
+        <v>127618438</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1209,16 +1219,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443203</v>
+        <v>443259</v>
       </c>
       <c r="R7" t="n">
-        <v>6767336</v>
+        <v>6767420</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,27 +1253,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,63 +1272,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127736014</v>
+        <v>127618474</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443188</v>
+        <v>443254</v>
       </c>
       <c r="R8" t="n">
-        <v>6767365</v>
+        <v>6767417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,27 +1354,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1383,26 +1380,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127736034</v>
+        <v>127618485</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1424,16 +1421,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443200</v>
+        <v>443251</v>
       </c>
       <c r="R9" t="n">
-        <v>6767341</v>
+        <v>6767415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,27 +1455,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,32 +1474,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127736032</v>
+        <v>127618498</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1531,16 +1522,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443208</v>
+        <v>443249</v>
       </c>
       <c r="R10" t="n">
-        <v>6767342</v>
+        <v>6767415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,27 +1556,22 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,63 +1580,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127736009</v>
+        <v>127618534</v>
       </c>
       <c r="B11" t="n">
-        <v>91748</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443242</v>
+        <v>443258</v>
       </c>
       <c r="R11" t="n">
-        <v>6767240</v>
+        <v>6767430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,27 +1662,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:57</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På 2 tallstammar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,32 +1686,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127736027</v>
+        <v>127619059</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1745,16 +1734,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oxeråsen S, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443195</v>
+        <v>443270</v>
       </c>
       <c r="R12" t="n">
-        <v>6767337</v>
+        <v>6767248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,27 +1768,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,32 +1787,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127785486</v>
+        <v>127723240</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1858,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443240</v>
+        <v>443268</v>
       </c>
       <c r="R13" t="n">
-        <v>6767312</v>
+        <v>6767195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,7 +1866,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1891,19 +1874,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,67 +1891,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127795268</v>
+        <v>127723241</v>
       </c>
       <c r="B14" t="n">
-        <v>91472</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443214</v>
+        <v>443271</v>
       </c>
       <c r="R14" t="n">
-        <v>6767263</v>
+        <v>6767202</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1997,7 +1963,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2016,22 +1982,4739 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127723242</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6767213</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127723244</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443265</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6767219</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127723245</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443267</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6767237</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127723246</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443273</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6767242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127723248</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443275</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6767256</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127723249</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6767269</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127723252</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443264</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6767298</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127723253</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>443258</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6767313</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127723254</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>443277</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6767303</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127723264</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>443266</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6767409</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127723266</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>443252</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6767410</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127723269</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>443225</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6767423</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127723271</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>443238</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6767435</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127730292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>443269</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6767232</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På 3 tallstammar</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127730308</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6767198</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127736025</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>443175</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6767298</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127736027</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>443195</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6767337</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127736030</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>443203</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6767336</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127736032</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>443208</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6767342</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127736034</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>443200</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6767341</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127785485</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>443269</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127785486</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>443240</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6767312</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127619016</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127722808</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>443273</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6767233</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127722809</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>443267</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6767259</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127619056</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127722899</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>443227</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6767432</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127618950</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>443268</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6767266</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127619053</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127722911</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6767269</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127723548</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>443276</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6767251</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127723549</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>443275</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6767256</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127730270</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>443273</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6767233</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack gamla</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127618987</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>443268</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6767266</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127619038</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127619035</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6767248</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127723614</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>443275</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6767256</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127722803</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6767291</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127618512</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>443254</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6767421</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127722967</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>443274</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6767205</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127722968</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>443270</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6767224</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127722971</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>443257</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6767415</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127722972</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>443230</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6767432</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127730354</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6767198</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På 3 rakor</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127736014</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>443188</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6767365</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127722924</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>443272</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6767292</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53426-2025 artfynd.xlsx
+++ b/artfynd/A 53426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795268</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618474</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618485</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618498</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618534</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619059</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723240</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723241</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723242</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723245</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2385,6 +2470,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723246</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2482,6 +2572,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723248</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2579,6 +2674,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723249</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723252</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2773,6 +2878,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723253</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2870,6 +2980,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723254</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2967,6 +3082,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723264</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723266</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723269</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723271</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3364,6 +3499,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730292</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3465,6 +3605,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730308</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3572,6 +3717,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3679,6 +3829,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3786,6 +3941,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736030</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3893,6 +4053,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4000,6 +4165,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736034</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4107,6 +4277,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785485</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4214,6 +4389,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785486</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4315,6 +4495,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619016</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4412,6 +4597,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722808</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4509,6 +4699,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722809</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4614,6 +4809,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619056</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4716,6 +4916,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722899</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4826,6 +5031,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618950</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4931,6 +5141,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619053</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5038,6 +5253,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722911</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5140,6 +5360,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723548</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5242,6 +5467,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723549</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5352,6 +5582,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730270</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5465,6 +5700,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618987</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5572,6 +5812,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619038</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5679,6 +5924,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127619035</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5781,6 +6031,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723614</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5883,6 +6138,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722803</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5990,6 +6250,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127618512</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6092,6 +6357,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722967</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6194,6 +6464,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722968</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6296,6 +6571,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722971</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6398,6 +6678,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722972</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6510,6 +6795,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127730354</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6618,6 +6908,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736014</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6715,8 +7010,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722924</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>